--- a/data/nzd0555/nzd0555.xlsx
+++ b/data/nzd0555/nzd0555.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J221"/>
+  <dimension ref="A1:J223"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8294,7 +8294,7 @@
         <v>294.1</v>
       </c>
       <c r="H221" t="n">
-        <v>290.35</v>
+        <v>293.13</v>
       </c>
       <c r="I221" t="n">
         <v>307</v>
@@ -8302,6 +8302,62 @@
       <c r="J221" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-29 22:20:17+00:00</t>
+        </is>
+      </c>
+      <c r="B222" t="n">
+        <v>238.05</v>
+      </c>
+      <c r="C222" t="inlineStr"/>
+      <c r="D222" t="inlineStr"/>
+      <c r="E222" t="inlineStr"/>
+      <c r="F222" t="inlineStr"/>
+      <c r="G222" t="n">
+        <v>278.14</v>
+      </c>
+      <c r="H222" t="n">
+        <v>283.11</v>
+      </c>
+      <c r="I222" t="n">
+        <v>284.77</v>
+      </c>
+      <c r="J222" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-15 22:19:54+00:00</t>
+        </is>
+      </c>
+      <c r="B223" t="n">
+        <v>218.48</v>
+      </c>
+      <c r="C223" t="inlineStr"/>
+      <c r="D223" t="inlineStr"/>
+      <c r="E223" t="inlineStr"/>
+      <c r="F223" t="inlineStr"/>
+      <c r="G223" t="n">
+        <v>278.14</v>
+      </c>
+      <c r="H223" t="n">
+        <v>283.11</v>
+      </c>
+      <c r="I223" t="n">
+        <v>284.77</v>
+      </c>
+      <c r="J223" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -8316,7 +8372,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B314"/>
+  <dimension ref="A1:B317"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11459,6 +11515,36 @@
       </c>
       <c r="B314" t="n">
         <v>0</v>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>2026-04-29 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B315" t="n">
+        <v>-0.09</v>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>2026-05-15 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B316" t="n">
+        <v>-0.15</v>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>2026-05-23 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B317" t="n">
+        <v>0.63</v>
       </c>
     </row>
   </sheetData>
@@ -11627,28 +11713,28 @@
         <v>0.0346</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.6004497023582585</v>
+        <v>-0.7013357521817238</v>
       </c>
       <c r="J2" t="n">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="K2" t="n">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="L2" t="n">
-        <v>0.06639871770958972</v>
+        <v>0.08288092791081492</v>
       </c>
       <c r="M2" t="n">
-        <v>13.5828087356699</v>
+        <v>14.07734314437616</v>
       </c>
       <c r="N2" t="n">
-        <v>301.9840354498073</v>
+        <v>328.1985838634648</v>
       </c>
       <c r="O2" t="n">
-        <v>17.37768786259574</v>
+        <v>18.11625192647378</v>
       </c>
       <c r="P2" t="n">
-        <v>300.0923795498716</v>
+        <v>301.0982720061361</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -11712,7 +11798,7 @@
         <v>0.3155283298477687</v>
       </c>
       <c r="J3" t="n">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="K3" t="n">
         <v>208</v>
@@ -11794,7 +11880,7 @@
         <v>-0.3507613891211495</v>
       </c>
       <c r="J4" t="n">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="K4" t="n">
         <v>216</v>
@@ -11872,7 +11958,7 @@
         <v>-0.3133115131170004</v>
       </c>
       <c r="J5" t="n">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="K5" t="n">
         <v>212</v>
@@ -11950,7 +12036,7 @@
         <v>-0.2888250913992032</v>
       </c>
       <c r="J6" t="n">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="K6" t="n">
         <v>215</v>
@@ -12025,28 +12111,28 @@
         <v>0.0585</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.4540507034917549</v>
+        <v>-0.4493862329119679</v>
       </c>
       <c r="J7" t="n">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="K7" t="n">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="L7" t="n">
-        <v>0.07093750484952344</v>
+        <v>0.07092762628310667</v>
       </c>
       <c r="M7" t="n">
-        <v>9.942740605887591</v>
+        <v>9.876686649658843</v>
       </c>
       <c r="N7" t="n">
-        <v>160.967554025977</v>
+        <v>159.5529475657994</v>
       </c>
       <c r="O7" t="n">
-        <v>12.68729892553876</v>
+        <v>12.63142698058297</v>
       </c>
       <c r="P7" t="n">
-        <v>287.6702282339493</v>
+        <v>287.6235529413171</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -12103,28 +12189,28 @@
         <v>0.0704</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.2411453454677512</v>
+        <v>-0.2331584834130898</v>
       </c>
       <c r="J8" t="n">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="K8" t="n">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="L8" t="n">
-        <v>0.02382203812779082</v>
+        <v>0.02270390453986837</v>
       </c>
       <c r="M8" t="n">
-        <v>8.758752699576918</v>
+        <v>8.717813532584819</v>
       </c>
       <c r="N8" t="n">
-        <v>142.0589072818023</v>
+        <v>141.1429658440408</v>
       </c>
       <c r="O8" t="n">
-        <v>11.9188467261645</v>
+        <v>11.88036050985157</v>
       </c>
       <c r="P8" t="n">
-        <v>286.3572233812432</v>
+        <v>286.2780732859476</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -12181,28 +12267,28 @@
         <v>0.0341</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.5004608049075189</v>
+        <v>-0.5110456581067044</v>
       </c>
       <c r="J9" t="n">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="K9" t="n">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="L9" t="n">
-        <v>0.04389673958678508</v>
+        <v>0.04656427049319867</v>
       </c>
       <c r="M9" t="n">
-        <v>14.2483299686663</v>
+        <v>14.17791522580253</v>
       </c>
       <c r="N9" t="n">
-        <v>330.1246791903041</v>
+        <v>327.4205153432325</v>
       </c>
       <c r="O9" t="n">
-        <v>18.16933348228008</v>
+        <v>18.0947648601255</v>
       </c>
       <c r="P9" t="n">
-        <v>304.2244914381944</v>
+        <v>304.3290247709239</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -12240,7 +12326,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J221"/>
+  <dimension ref="A1:J223"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23525,7 +23611,7 @@
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>-46.62257397606013,169.2811268465853</t>
+          <t>-46.62259885811334,169.28112342764788</t>
         </is>
       </c>
       <c r="I221" t="inlineStr">
@@ -23536,6 +23622,78 @@
       <c r="J221" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-29 22:20:17+00:00</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>-46.622334999012274,169.2865706906326</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr"/>
+      <c r="D222" t="inlineStr"/>
+      <c r="E222" t="inlineStr"/>
+      <c r="F222" t="inlineStr"/>
+      <c r="G222" t="inlineStr">
+        <is>
+          <t>-46.62250288040288,169.28203845421646</t>
+        </is>
+      </c>
+      <c r="H222" t="inlineStr">
+        <is>
+          <t>-46.62250917531595,169.28113575056256</t>
+        </is>
+      </c>
+      <c r="I222" t="inlineStr">
+        <is>
+          <t>-46.62248584437464,169.28023711697583</t>
+        </is>
+      </c>
+      <c r="J222" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-15 22:19:54+00:00</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>-46.62215983877987,169.28659474615174</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr"/>
+      <c r="D223" t="inlineStr"/>
+      <c r="E223" t="inlineStr"/>
+      <c r="F223" t="inlineStr"/>
+      <c r="G223" t="inlineStr">
+        <is>
+          <t>-46.62250288040288,169.28203845421646</t>
+        </is>
+      </c>
+      <c r="H223" t="inlineStr">
+        <is>
+          <t>-46.62250917531595,169.28113575056256</t>
+        </is>
+      </c>
+      <c r="I223" t="inlineStr">
+        <is>
+          <t>-46.62248584437464,169.28023711697583</t>
+        </is>
+      </c>
+      <c r="J223" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>

--- a/data/nzd0555/nzd0555.xlsx
+++ b/data/nzd0555/nzd0555.xlsx
@@ -8372,7 +8372,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B317"/>
+  <dimension ref="A1:B318"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11545,6 +11545,16 @@
       </c>
       <c r="B317" t="n">
         <v>0.63</v>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>2026-06-08 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B318" t="n">
+        <v>0.49</v>
       </c>
     </row>
   </sheetData>
